--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$98</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="204">
   <si>
     <t>S No</t>
   </si>
@@ -788,6 +788,12 @@
   </si>
   <si>
     <t>2500/- for subscription + 2500/- for Family meet + 2024 Urbaser 2026 pongalfest</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Nandakumar</t>
   </si>
 </sst>
 </file>
@@ -985,7 +991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1088,6 +1094,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,7 +1378,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:Q117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1379,12 +1386,12 @@
     <col min="3" max="5" width="30.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" style="23" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" style="23" customWidth="1"/>
-    <col min="8" max="10" width="17.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="45.5703125" style="26" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
+    <col min="8" max="11" width="17.7109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="45.5703125" style="26" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,11 +1422,14 @@
       <c r="J1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1450,14 +1460,17 @@
       <c r="J2" s="18">
         <v>2500</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
+      <c r="K2" s="36">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="10"/>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
-      <c r="P2" s="12"/>
-    </row>
-    <row r="3" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P2" s="11"/>
+      <c r="Q2" s="12"/>
+    </row>
+    <row r="3" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
@@ -1489,16 +1502,19 @@
       <c r="J3" s="18">
         <v>7500</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="36">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
+      <c r="M3" s="10"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="12"/>
-    </row>
-    <row r="4" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P3" s="11"/>
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1530,15 +1546,18 @@
       <c r="J4" s="35">
         <v>0</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="36">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
+      <c r="M4" s="10"/>
       <c r="N4" s="11"/>
-      <c r="P4" s="12"/>
-    </row>
-    <row r="5" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="11"/>
+      <c r="Q4" s="12"/>
+    </row>
+    <row r="5" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1568,13 +1587,16 @@
       <c r="J5" s="9">
         <v>10000</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
+      <c r="K5" s="36">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
       <c r="N5" s="11"/>
-      <c r="P5" s="12"/>
-    </row>
-    <row r="6" spans="1:16" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="O5" s="11"/>
+      <c r="Q5" s="12"/>
+    </row>
+    <row r="6" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1606,14 +1628,17 @@
       <c r="J6" s="18">
         <v>15000</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
+      <c r="K6" s="36">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="10"/>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
-      <c r="P6" s="12"/>
-    </row>
-    <row r="7" spans="1:16" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="12"/>
+    </row>
+    <row r="7" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1645,16 +1670,19 @@
       <c r="J7" s="8">
         <v>1500</v>
       </c>
-      <c r="K7" s="49" t="s">
+      <c r="K7" s="36">
+        <v>0</v>
+      </c>
+      <c r="L7" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
+      <c r="M7" s="10"/>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
-      <c r="P7" s="12"/>
-    </row>
-    <row r="8" spans="1:16" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="P7" s="11"/>
+      <c r="Q7" s="12"/>
+    </row>
+    <row r="8" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1686,14 +1714,17 @@
       <c r="J8" s="9">
         <v>2500</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11"/>
+      <c r="K8" s="36">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="10"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
-      <c r="P8" s="12"/>
-    </row>
-    <row r="9" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="12"/>
+    </row>
+    <row r="9" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1725,14 +1756,17 @@
       <c r="J9" s="35">
         <v>0</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11"/>
+      <c r="K9" s="36">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9"/>
+      <c r="M9" s="10"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
-      <c r="P9" s="12"/>
-    </row>
-    <row r="10" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
+    </row>
+    <row r="10" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1762,14 +1796,17 @@
       <c r="J10" s="9">
         <v>7500</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11"/>
+      <c r="K10" s="36">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9"/>
+      <c r="M10" s="10"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
-      <c r="P10" s="12"/>
-    </row>
-    <row r="11" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
+    </row>
+    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1801,14 +1838,17 @@
       <c r="J11" s="9">
         <v>2500</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
+      <c r="K11" s="36">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9"/>
+      <c r="M11" s="10"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
-      <c r="P11" s="12"/>
-    </row>
-    <row r="12" spans="1:16" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="P11" s="11"/>
+      <c r="Q11" s="12"/>
+    </row>
+    <row r="12" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1840,16 +1880,19 @@
       <c r="J12" s="8">
         <v>2500</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="36">
+        <v>0</v>
+      </c>
+      <c r="L12" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="11"/>
+      <c r="M12" s="10"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
-      <c r="P12" s="12"/>
-    </row>
-    <row r="13" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P12" s="11"/>
+      <c r="Q12" s="12"/>
+    </row>
+    <row r="13" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1881,16 +1924,19 @@
       <c r="J13" s="9">
         <v>7500</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="9">
+        <v>2500</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="11"/>
+      <c r="M13" s="10"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1922,16 +1968,19 @@
       <c r="J14" s="25">
         <v>2500</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="36">
+        <v>0</v>
+      </c>
+      <c r="L14" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="11"/>
+      <c r="M14" s="10"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="12"/>
-    </row>
-    <row r="15" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="11"/>
+      <c r="Q14" s="12"/>
+    </row>
+    <row r="15" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1963,14 +2012,17 @@
       <c r="J15" s="9">
         <v>1500</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="11"/>
+      <c r="K15" s="36">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="10"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="11"/>
+      <c r="Q15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1994,14 +2046,17 @@
       <c r="J16" s="9">
         <v>1500</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="11"/>
+      <c r="K16" s="36">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9"/>
+      <c r="M16" s="10"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="12"/>
-    </row>
-    <row r="17" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="11"/>
+      <c r="Q16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2025,14 +2080,17 @@
       <c r="J17" s="9">
         <v>1500</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="11"/>
+      <c r="K17" s="36">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="10"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="12"/>
-    </row>
-    <row r="18" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="11"/>
+      <c r="Q17" s="12"/>
+    </row>
+    <row r="18" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2064,14 +2122,17 @@
       <c r="J18" s="35">
         <v>0</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="11"/>
+      <c r="K18" s="36">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="10"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
-      <c r="P18" s="12"/>
-    </row>
-    <row r="19" spans="1:16" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P18" s="11"/>
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2103,14 +2164,17 @@
       <c r="J19" s="20">
         <v>0</v>
       </c>
-      <c r="K19" s="24"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="11"/>
+      <c r="K19" s="36">
+        <v>0</v>
+      </c>
+      <c r="L19" s="24"/>
+      <c r="M19" s="10"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
-      <c r="P19" s="12"/>
-    </row>
-    <row r="20" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="11"/>
+      <c r="Q19" s="12"/>
+    </row>
+    <row r="20" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2134,14 +2198,17 @@
       <c r="J20" s="8">
         <v>1500</v>
       </c>
-      <c r="K20" s="50"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="11"/>
+      <c r="K20" s="36">
+        <v>0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="M20" s="10"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
-      <c r="P20" s="12"/>
-    </row>
-    <row r="21" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P20" s="11"/>
+      <c r="Q20" s="12"/>
+    </row>
+    <row r="21" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2173,14 +2240,17 @@
       <c r="J21" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="11"/>
+      <c r="K21" s="36">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
-      <c r="P21" s="12"/>
-    </row>
-    <row r="22" spans="1:16" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P21" s="11"/>
+      <c r="Q21" s="12"/>
+    </row>
+    <row r="22" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2212,16 +2282,19 @@
       <c r="J22" s="18">
         <v>2500</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="36">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="11"/>
+      <c r="M22" s="10"/>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="12"/>
-    </row>
-    <row r="23" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P22" s="11"/>
+      <c r="Q22" s="12"/>
+    </row>
+    <row r="23" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2253,14 +2326,17 @@
       <c r="J23" s="9">
         <v>1500</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="11"/>
+      <c r="K23" s="36">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="10"/>
       <c r="N23" s="11"/>
       <c r="O23" s="11"/>
-      <c r="P23" s="12"/>
-    </row>
-    <row r="24" spans="1:16" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P23" s="11"/>
+      <c r="Q23" s="12"/>
+    </row>
+    <row r="24" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2292,14 +2368,17 @@
       <c r="J24" s="18">
         <v>7500</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="11"/>
+      <c r="K24" s="36">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="10"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
-      <c r="P24" s="12"/>
-    </row>
-    <row r="25" spans="1:16" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="P24" s="11"/>
+      <c r="Q24" s="12"/>
+    </row>
+    <row r="25" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2331,14 +2410,17 @@
       <c r="J25" s="20">
         <v>0</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="11"/>
+      <c r="K25" s="36">
+        <v>0</v>
+      </c>
+      <c r="L25" s="24"/>
+      <c r="M25" s="10"/>
       <c r="N25" s="11"/>
       <c r="O25" s="11"/>
-      <c r="P25" s="12"/>
-    </row>
-    <row r="26" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="11"/>
+      <c r="Q25" s="12"/>
+    </row>
+    <row r="26" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2370,14 +2452,17 @@
       <c r="J26" s="20">
         <v>0</v>
       </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="11"/>
+      <c r="K26" s="36">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9"/>
+      <c r="M26" s="10"/>
       <c r="N26" s="11"/>
       <c r="O26" s="11"/>
-      <c r="P26" s="12"/>
-    </row>
-    <row r="27" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="11"/>
+      <c r="Q26" s="12"/>
+    </row>
+    <row r="27" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2409,14 +2494,17 @@
       <c r="J27" s="18">
         <v>2500</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="11"/>
+      <c r="K27" s="36">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9"/>
+      <c r="M27" s="10"/>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
-      <c r="P27" s="12"/>
-    </row>
-    <row r="28" spans="1:16" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="P27" s="11"/>
+      <c r="Q27" s="12"/>
+    </row>
+    <row r="28" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2448,14 +2536,17 @@
       <c r="J28" s="9">
         <v>2500</v>
       </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="11"/>
+      <c r="K28" s="36">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9"/>
+      <c r="M28" s="10"/>
       <c r="N28" s="11"/>
       <c r="O28" s="11"/>
-      <c r="P28" s="12"/>
-    </row>
-    <row r="29" spans="1:16" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="P28" s="11"/>
+      <c r="Q28" s="12"/>
+    </row>
+    <row r="29" spans="1:17" s="13" customFormat="1" ht="32.25" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2487,14 +2578,17 @@
       <c r="J29" s="9">
         <v>2500</v>
       </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="11"/>
+      <c r="K29" s="36">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9"/>
+      <c r="M29" s="10"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="12"/>
-    </row>
-    <row r="30" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P29" s="11"/>
+      <c r="Q29" s="12"/>
+    </row>
+    <row r="30" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2514,14 +2608,17 @@
       <c r="J30" s="9">
         <v>7500</v>
       </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="11"/>
+      <c r="K30" s="36">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="10"/>
       <c r="N30" s="11"/>
       <c r="O30" s="11"/>
-      <c r="P30" s="12"/>
-    </row>
-    <row r="31" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P30" s="11"/>
+      <c r="Q30" s="12"/>
+    </row>
+    <row r="31" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2553,16 +2650,19 @@
       <c r="J31" s="8">
         <v>5000</v>
       </c>
-      <c r="K31" s="24" t="s">
+      <c r="K31" s="36">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="11"/>
+      <c r="M31" s="10"/>
       <c r="N31" s="11"/>
       <c r="O31" s="11"/>
-      <c r="P31" s="12"/>
-    </row>
-    <row r="32" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P31" s="11"/>
+      <c r="Q31" s="12"/>
+    </row>
+    <row r="32" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2594,14 +2694,17 @@
       <c r="J32" s="22">
         <v>1500</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="11"/>
+      <c r="K32" s="36">
+        <v>0</v>
+      </c>
+      <c r="L32" s="24"/>
+      <c r="M32" s="10"/>
       <c r="N32" s="11"/>
       <c r="O32" s="11"/>
-      <c r="P32" s="12"/>
-    </row>
-    <row r="33" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P32" s="11"/>
+      <c r="Q32" s="12"/>
+    </row>
+    <row r="33" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2633,14 +2736,17 @@
       <c r="J33" s="8">
         <v>1500</v>
       </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="11"/>
+      <c r="K33" s="36">
+        <v>0</v>
+      </c>
+      <c r="L33" s="24"/>
+      <c r="M33" s="10"/>
       <c r="N33" s="11"/>
       <c r="O33" s="11"/>
-      <c r="P33" s="12"/>
-    </row>
-    <row r="34" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P33" s="11"/>
+      <c r="Q33" s="12"/>
+    </row>
+    <row r="34" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2672,14 +2778,17 @@
       <c r="J34" s="8">
         <v>1500</v>
       </c>
-      <c r="K34" s="24"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="11"/>
+      <c r="K34" s="36">
+        <v>0</v>
+      </c>
+      <c r="L34" s="24"/>
+      <c r="M34" s="10"/>
       <c r="N34" s="11"/>
       <c r="O34" s="11"/>
-      <c r="P34" s="12"/>
-    </row>
-    <row r="35" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P34" s="11"/>
+      <c r="Q34" s="12"/>
+    </row>
+    <row r="35" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" ref="A35:A66" si="1">A34+1</f>
         <v>34</v>
@@ -2711,14 +2820,17 @@
       <c r="J35" s="8">
         <v>1500</v>
       </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="11"/>
+      <c r="K35" s="36">
+        <v>0</v>
+      </c>
+      <c r="L35" s="24"/>
+      <c r="M35" s="10"/>
       <c r="N35" s="11"/>
       <c r="O35" s="11"/>
-      <c r="P35" s="12"/>
-    </row>
-    <row r="36" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P35" s="11"/>
+      <c r="Q35" s="12"/>
+    </row>
+    <row r="36" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -2750,14 +2862,17 @@
       <c r="J36" s="20">
         <v>0</v>
       </c>
-      <c r="K36" s="24"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="11"/>
+      <c r="K36" s="36">
+        <v>0</v>
+      </c>
+      <c r="L36" s="24"/>
+      <c r="M36" s="10"/>
       <c r="N36" s="11"/>
       <c r="O36" s="11"/>
-      <c r="P36" s="12"/>
-    </row>
-    <row r="37" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P36" s="11"/>
+      <c r="Q36" s="12"/>
+    </row>
+    <row r="37" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -2773,14 +2888,17 @@
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
       <c r="J37" s="38"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="11"/>
+      <c r="K37" s="36">
+        <v>0</v>
+      </c>
+      <c r="L37" s="44"/>
+      <c r="M37" s="10"/>
       <c r="N37" s="11"/>
       <c r="O37" s="11"/>
-      <c r="P37" s="12"/>
-    </row>
-    <row r="38" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P37" s="11"/>
+      <c r="Q37" s="12"/>
+    </row>
+    <row r="38" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -2812,16 +2930,19 @@
       <c r="J38" s="9">
         <v>12500</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="36">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="11"/>
+      <c r="M38" s="10"/>
       <c r="N38" s="11"/>
       <c r="O38" s="11"/>
-      <c r="P38" s="12"/>
-    </row>
-    <row r="39" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P38" s="11"/>
+      <c r="Q38" s="12"/>
+    </row>
+    <row r="39" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -2853,16 +2974,19 @@
       <c r="J39" s="18">
         <v>2500</v>
       </c>
-      <c r="K39" s="9" t="s">
+      <c r="K39" s="36">
+        <v>0</v>
+      </c>
+      <c r="L39" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="11"/>
+      <c r="M39" s="10"/>
       <c r="N39" s="11"/>
       <c r="O39" s="11"/>
-      <c r="P39" s="12"/>
-    </row>
-    <row r="40" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P39" s="11"/>
+      <c r="Q39" s="12"/>
+    </row>
+    <row r="40" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2894,16 +3018,19 @@
       <c r="J40" s="9">
         <v>7500</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="36">
+        <v>0</v>
+      </c>
+      <c r="L40" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="11"/>
+      <c r="M40" s="10"/>
       <c r="N40" s="11"/>
       <c r="O40" s="11"/>
-      <c r="P40" s="12"/>
-    </row>
-    <row r="41" spans="1:16" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P40" s="11"/>
+      <c r="Q40" s="12"/>
+    </row>
+    <row r="41" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2919,14 +3046,17 @@
       <c r="H41" s="43"/>
       <c r="I41" s="43"/>
       <c r="J41" s="43"/>
-      <c r="K41" s="42"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="11"/>
+      <c r="K41" s="36">
+        <v>0</v>
+      </c>
+      <c r="L41" s="42"/>
+      <c r="M41" s="10"/>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
-      <c r="P41" s="12"/>
-    </row>
-    <row r="42" spans="1:16" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P41" s="11"/>
+      <c r="Q41" s="12"/>
+    </row>
+    <row r="42" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2942,14 +3072,17 @@
       <c r="H42" s="43"/>
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="11"/>
+      <c r="K42" s="36">
+        <v>0</v>
+      </c>
+      <c r="L42" s="42"/>
+      <c r="M42" s="10"/>
       <c r="N42" s="11"/>
       <c r="O42" s="11"/>
-      <c r="P42" s="12"/>
-    </row>
-    <row r="43" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P42" s="11"/>
+      <c r="Q42" s="12"/>
+    </row>
+    <row r="43" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -2981,14 +3114,17 @@
       <c r="J43" s="9">
         <v>7500</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="11"/>
+      <c r="K43" s="36">
+        <v>0</v>
+      </c>
+      <c r="L43" s="9"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="11"/>
       <c r="O43" s="11"/>
-      <c r="P43" s="12"/>
-    </row>
-    <row r="44" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P43" s="11"/>
+      <c r="Q43" s="12"/>
+    </row>
+    <row r="44" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -3017,17 +3153,20 @@
       <c r="I44" s="9">
         <v>7500</v>
       </c>
-      <c r="J44" s="35">
-        <v>0</v>
-      </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="11"/>
+      <c r="J44" s="9">
+        <v>7500</v>
+      </c>
+      <c r="K44" s="36">
+        <v>0</v>
+      </c>
+      <c r="L44" s="9"/>
+      <c r="M44" s="10"/>
       <c r="N44" s="11"/>
       <c r="O44" s="11"/>
-      <c r="P44" s="12"/>
-    </row>
-    <row r="45" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P44" s="11"/>
+      <c r="Q44" s="12"/>
+    </row>
+    <row r="45" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -3059,16 +3198,19 @@
       <c r="J45" s="9">
         <v>7500</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="K45" s="36">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="11"/>
+      <c r="M45" s="10"/>
       <c r="N45" s="11"/>
       <c r="O45" s="11"/>
-      <c r="P45" s="12"/>
-    </row>
-    <row r="46" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P45" s="11"/>
+      <c r="Q45" s="12"/>
+    </row>
+    <row r="46" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -3100,14 +3242,17 @@
       <c r="J46" s="9">
         <v>2500</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="11"/>
+      <c r="K46" s="36">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
-      <c r="P46" s="12"/>
-    </row>
-    <row r="47" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P46" s="11"/>
+      <c r="Q46" s="12"/>
+    </row>
+    <row r="47" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -3139,14 +3284,17 @@
       <c r="J47" s="18">
         <v>2500</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="11"/>
+      <c r="K47" s="36">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9"/>
+      <c r="M47" s="10"/>
       <c r="N47" s="11"/>
       <c r="O47" s="11"/>
-      <c r="P47" s="12"/>
-    </row>
-    <row r="48" spans="1:16" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P47" s="11"/>
+      <c r="Q47" s="12"/>
+    </row>
+    <row r="48" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -3178,14 +3326,17 @@
       <c r="J48" s="9">
         <v>2500</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="11"/>
+      <c r="K48" s="36">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9"/>
+      <c r="M48" s="10"/>
       <c r="N48" s="11"/>
       <c r="O48" s="11"/>
-      <c r="P48" s="12"/>
-    </row>
-    <row r="49" spans="1:16" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P48" s="11"/>
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -3217,14 +3368,17 @@
       <c r="J49" s="9">
         <v>2500</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="11"/>
+      <c r="K49" s="36">
+        <v>0</v>
+      </c>
+      <c r="L49" s="9"/>
+      <c r="M49" s="10"/>
       <c r="N49" s="11"/>
       <c r="O49" s="11"/>
-      <c r="P49" s="12"/>
-    </row>
-    <row r="50" spans="1:16" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="P49" s="11"/>
+      <c r="Q49" s="12"/>
+    </row>
+    <row r="50" spans="1:17" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -3256,14 +3410,17 @@
       <c r="J50" s="35">
         <v>0</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="11"/>
+      <c r="K50" s="36">
+        <v>0</v>
+      </c>
+      <c r="L50" s="9"/>
+      <c r="M50" s="10"/>
       <c r="N50" s="11"/>
       <c r="O50" s="11"/>
-      <c r="P50" s="12"/>
-    </row>
-    <row r="51" spans="1:16" s="13" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P50" s="11"/>
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51" spans="1:17" s="13" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -3295,14 +3452,17 @@
       <c r="J51" s="36">
         <v>0</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="11"/>
+      <c r="K51" s="36">
+        <v>0</v>
+      </c>
+      <c r="L51" s="9"/>
+      <c r="M51" s="10"/>
       <c r="N51" s="11"/>
       <c r="O51" s="11"/>
-      <c r="P51" s="12"/>
-    </row>
-    <row r="52" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P51" s="11"/>
+      <c r="Q51" s="12"/>
+    </row>
+    <row r="52" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -3334,14 +3494,17 @@
       <c r="J52" s="8">
         <v>2500</v>
       </c>
-      <c r="K52" s="24"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="11"/>
+      <c r="K52" s="36">
+        <v>0</v>
+      </c>
+      <c r="L52" s="24"/>
+      <c r="M52" s="10"/>
       <c r="N52" s="11"/>
       <c r="O52" s="11"/>
-      <c r="P52" s="12"/>
-    </row>
-    <row r="53" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P52" s="11"/>
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -3373,14 +3536,17 @@
       <c r="J53" s="8">
         <v>2500</v>
       </c>
-      <c r="K53" s="24"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="11"/>
+      <c r="K53" s="36">
+        <v>0</v>
+      </c>
+      <c r="L53" s="24"/>
+      <c r="M53" s="10"/>
       <c r="N53" s="11"/>
       <c r="O53" s="11"/>
-      <c r="P53" s="12"/>
-    </row>
-    <row r="54" spans="1:16" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P53" s="11"/>
+      <c r="Q53" s="12"/>
+    </row>
+    <row r="54" spans="1:17" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="47">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3412,14 +3578,17 @@
       <c r="J54" s="8">
         <v>2500</v>
       </c>
-      <c r="K54" s="24"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="11"/>
+      <c r="K54" s="8">
+        <v>2500</v>
+      </c>
+      <c r="L54" s="24"/>
+      <c r="M54" s="10"/>
       <c r="N54" s="11"/>
       <c r="O54" s="11"/>
-      <c r="P54" s="12"/>
-    </row>
-    <row r="55" spans="1:16" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="P54" s="11"/>
+      <c r="Q54" s="12"/>
+    </row>
+    <row r="55" spans="1:17" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3451,16 +3620,19 @@
       <c r="J55" s="8">
         <v>7500</v>
       </c>
-      <c r="K55" s="24" t="s">
+      <c r="K55" s="36">
+        <v>0</v>
+      </c>
+      <c r="L55" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="L55" s="10"/>
-      <c r="M55" s="11"/>
+      <c r="M55" s="10"/>
       <c r="N55" s="11"/>
       <c r="O55" s="11"/>
-      <c r="P55" s="12"/>
-    </row>
-    <row r="56" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P55" s="11"/>
+      <c r="Q55" s="12"/>
+    </row>
+    <row r="56" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3492,16 +3664,19 @@
       <c r="J56" s="20">
         <v>1500</v>
       </c>
-      <c r="K56" s="24" t="s">
+      <c r="K56" s="36">
+        <v>0</v>
+      </c>
+      <c r="L56" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="L56" s="10"/>
-      <c r="M56" s="11"/>
+      <c r="M56" s="10"/>
       <c r="N56" s="11"/>
       <c r="O56" s="11"/>
-      <c r="P56" s="12"/>
-    </row>
-    <row r="57" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P56" s="11"/>
+      <c r="Q56" s="12"/>
+    </row>
+    <row r="57" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3533,14 +3708,17 @@
       <c r="J57" s="20">
         <v>0</v>
       </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="11"/>
+      <c r="K57" s="36">
+        <v>0</v>
+      </c>
+      <c r="L57" s="9"/>
+      <c r="M57" s="10"/>
       <c r="N57" s="11"/>
       <c r="O57" s="11"/>
-      <c r="P57" s="12"/>
-    </row>
-    <row r="58" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P57" s="11"/>
+      <c r="Q57" s="12"/>
+    </row>
+    <row r="58" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -3556,14 +3734,17 @@
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
       <c r="J58" s="38"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="11"/>
+      <c r="K58" s="36">
+        <v>0</v>
+      </c>
+      <c r="L58" s="44"/>
+      <c r="M58" s="10"/>
       <c r="N58" s="11"/>
       <c r="O58" s="11"/>
-      <c r="P58" s="12"/>
-    </row>
-    <row r="59" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P58" s="11"/>
+      <c r="Q58" s="12"/>
+    </row>
+    <row r="59" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <f t="shared" si="1"/>
         <v>58</v>
@@ -3579,14 +3760,17 @@
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
-      <c r="K59" s="44"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="11"/>
+      <c r="K59" s="36">
+        <v>0</v>
+      </c>
+      <c r="L59" s="44"/>
+      <c r="M59" s="10"/>
       <c r="N59" s="11"/>
       <c r="O59" s="11"/>
-      <c r="P59" s="12"/>
-    </row>
-    <row r="60" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P59" s="11"/>
+      <c r="Q59" s="12"/>
+    </row>
+    <row r="60" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -3602,14 +3786,17 @@
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
-      <c r="K60" s="44"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="11"/>
+      <c r="K60" s="36">
+        <v>0</v>
+      </c>
+      <c r="L60" s="44"/>
+      <c r="M60" s="10"/>
       <c r="N60" s="11"/>
       <c r="O60" s="11"/>
-      <c r="P60" s="12"/>
-    </row>
-    <row r="61" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P60" s="11"/>
+      <c r="Q60" s="12"/>
+    </row>
+    <row r="61" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -3638,17 +3825,20 @@
       <c r="I61" s="18">
         <v>2500</v>
       </c>
-      <c r="J61" s="36">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="11"/>
+      <c r="J61" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K61" s="36">
+        <v>0</v>
+      </c>
+      <c r="L61" s="9"/>
+      <c r="M61" s="10"/>
       <c r="N61" s="11"/>
       <c r="O61" s="11"/>
-      <c r="P61" s="12"/>
-    </row>
-    <row r="62" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P61" s="11"/>
+      <c r="Q61" s="12"/>
+    </row>
+    <row r="62" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -3663,7 +3853,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="48" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F62" s="16">
         <v>0</v>
@@ -3680,14 +3870,17 @@
       <c r="J62" s="17">
         <v>0</v>
       </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="11"/>
+      <c r="K62" s="16">
+        <v>1500</v>
+      </c>
+      <c r="L62" s="9"/>
+      <c r="M62" s="10"/>
       <c r="N62" s="11"/>
       <c r="O62" s="11"/>
-      <c r="P62" s="12"/>
-    </row>
-    <row r="63" spans="1:16" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="P62" s="11"/>
+      <c r="Q62" s="12"/>
+    </row>
+    <row r="63" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -3719,14 +3912,17 @@
       <c r="J63" s="36">
         <v>0</v>
       </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="11"/>
+      <c r="K63" s="36">
+        <v>0</v>
+      </c>
+      <c r="L63" s="9"/>
+      <c r="M63" s="10"/>
       <c r="N63" s="11"/>
       <c r="O63" s="11"/>
-      <c r="P63" s="12"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P63" s="11"/>
+      <c r="Q63" s="12"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -3758,9 +3954,12 @@
       <c r="J64" s="9">
         <v>2500</v>
       </c>
-      <c r="K64" s="9"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K64" s="36">
+        <v>0</v>
+      </c>
+      <c r="L64" s="9"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -3792,41 +3991,47 @@
       <c r="J65" s="36">
         <v>0</v>
       </c>
-      <c r="K65" s="9"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="39">
+      <c r="K65" s="36">
+        <v>0</v>
+      </c>
+      <c r="L65" s="9"/>
+    </row>
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="55">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="B66" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C66" s="40" t="s">
+      <c r="B66" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="D66" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F66" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="D66" s="41" t="s">
+      <c r="G66" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="E66" s="41" t="s">
+      <c r="H66" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="F66" s="38" t="s">
+      <c r="I66" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="G66" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H66" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="I66" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="J66" s="38"/>
-      <c r="K66" s="44"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J66" s="56"/>
+      <c r="K66" s="8">
+        <v>1500</v>
+      </c>
+      <c r="L66" s="50"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <f t="shared" ref="A67:A99" si="2">A66+1</f>
         <v>66</v>
@@ -3858,9 +4063,12 @@
       <c r="J67" s="8">
         <v>2500</v>
       </c>
-      <c r="K67" s="24"/>
-    </row>
-    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K67" s="36">
+        <v>0</v>
+      </c>
+      <c r="L67" s="24"/>
+    </row>
+    <row r="68" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3892,9 +4100,12 @@
       <c r="J68" s="8">
         <v>2500</v>
       </c>
-      <c r="K68" s="24"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K68" s="36">
+        <v>0</v>
+      </c>
+      <c r="L68" s="24"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="46">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3926,9 +4137,12 @@
       <c r="J69" s="8">
         <v>2500</v>
       </c>
-      <c r="K69" s="9"/>
-    </row>
-    <row r="70" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="K69" s="36">
+        <v>0</v>
+      </c>
+      <c r="L69" s="9"/>
+    </row>
+    <row r="70" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3960,11 +4174,14 @@
       <c r="J70" s="9">
         <v>25000</v>
       </c>
-      <c r="K70" s="9" t="s">
+      <c r="K70" s="36">
+        <v>0</v>
+      </c>
+      <c r="L70" s="9" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3996,9 +4213,12 @@
       <c r="J71" s="18">
         <v>10000</v>
       </c>
-      <c r="K71" s="9"/>
-    </row>
-    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K71" s="36">
+        <v>0</v>
+      </c>
+      <c r="L71" s="9"/>
+    </row>
+    <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -4030,9 +4250,12 @@
       <c r="J72" s="9">
         <v>1500</v>
       </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K72" s="36">
+        <v>0</v>
+      </c>
+      <c r="L72" s="9"/>
+    </row>
+    <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -4056,9 +4279,12 @@
       <c r="J73" s="9">
         <v>1500</v>
       </c>
-      <c r="K73" s="9"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K73" s="36">
+        <v>0</v>
+      </c>
+      <c r="L73" s="9"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -4088,9 +4314,12 @@
       <c r="J74" s="35">
         <v>0</v>
       </c>
-      <c r="K74" s="9"/>
-    </row>
-    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K74" s="36">
+        <v>0</v>
+      </c>
+      <c r="L74" s="9"/>
+    </row>
+    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -4122,9 +4351,12 @@
       <c r="J75" s="9">
         <v>10000</v>
       </c>
-      <c r="K75" s="9"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K75" s="36">
+        <v>0</v>
+      </c>
+      <c r="L75" s="9"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -4156,9 +4388,12 @@
       <c r="J76" s="35">
         <v>0</v>
       </c>
-      <c r="K76" s="9"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K76" s="36">
+        <v>0</v>
+      </c>
+      <c r="L76" s="9"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -4190,9 +4425,12 @@
       <c r="J77" s="36">
         <v>0</v>
       </c>
-      <c r="K77" s="9"/>
-    </row>
-    <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="K77" s="36">
+        <v>0</v>
+      </c>
+      <c r="L77" s="9"/>
+    </row>
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -4224,9 +4462,12 @@
       <c r="J78" s="18">
         <v>10000</v>
       </c>
-      <c r="K78" s="9"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K78" s="36">
+        <v>0</v>
+      </c>
+      <c r="L78" s="9"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -4258,9 +4499,12 @@
       <c r="J79" s="35">
         <v>0</v>
       </c>
-      <c r="K79" s="9"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K79" s="36">
+        <v>0</v>
+      </c>
+      <c r="L79" s="9"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <f t="shared" si="2"/>
         <v>79</v>
@@ -4276,9 +4520,12 @@
       <c r="H80" s="42"/>
       <c r="I80" s="42"/>
       <c r="J80" s="42"/>
-      <c r="K80" s="42"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K80" s="36">
+        <v>0</v>
+      </c>
+      <c r="L80" s="42"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -4308,9 +4555,12 @@
         <v>159</v>
       </c>
       <c r="J81" s="42"/>
-      <c r="K81" s="42"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K81" s="36">
+        <v>0</v>
+      </c>
+      <c r="L81" s="42"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4326,9 +4576,12 @@
       <c r="H82" s="42"/>
       <c r="I82" s="42"/>
       <c r="J82" s="42"/>
-      <c r="K82" s="42"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K82" s="36">
+        <v>0</v>
+      </c>
+      <c r="L82" s="42"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4360,9 +4613,12 @@
       <c r="J83" s="18">
         <v>2500</v>
       </c>
-      <c r="K83" s="9"/>
-    </row>
-    <row r="84" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K83" s="36">
+        <v>0</v>
+      </c>
+      <c r="L83" s="9"/>
+    </row>
+    <row r="84" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4390,11 +4646,14 @@
       <c r="J84" s="9">
         <v>12500</v>
       </c>
-      <c r="K84" s="9" t="s">
+      <c r="K84" s="36">
+        <v>0</v>
+      </c>
+      <c r="L84" s="9" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4426,11 +4685,14 @@
       <c r="J85" s="36">
         <v>0</v>
       </c>
-      <c r="K85" s="9" t="s">
+      <c r="K85" s="36">
+        <v>0</v>
+      </c>
+      <c r="L85" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4462,9 +4724,12 @@
       <c r="J86" s="18">
         <v>15000</v>
       </c>
-      <c r="K86" s="9"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K86" s="36">
+        <v>0</v>
+      </c>
+      <c r="L86" s="9"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4496,11 +4761,14 @@
       <c r="J87" s="9">
         <v>2500</v>
       </c>
-      <c r="K87" s="9" t="s">
+      <c r="K87" s="36">
+        <v>0</v>
+      </c>
+      <c r="L87" s="9" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4532,9 +4800,12 @@
       <c r="J88" s="35">
         <v>0</v>
       </c>
-      <c r="K88" s="9"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K88" s="36">
+        <v>0</v>
+      </c>
+      <c r="L88" s="9"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -4566,9 +4837,12 @@
       <c r="J89" s="35">
         <v>0</v>
       </c>
-      <c r="K89" s="9"/>
-    </row>
-    <row r="90" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="K89" s="36">
+        <v>0</v>
+      </c>
+      <c r="L89" s="9"/>
+    </row>
+    <row r="90" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -4600,9 +4874,12 @@
       <c r="J90" s="8">
         <v>7500</v>
       </c>
-      <c r="K90" s="24"/>
-    </row>
-    <row r="91" spans="1:11" ht="195" x14ac:dyDescent="0.25">
+      <c r="K90" s="36">
+        <v>0</v>
+      </c>
+      <c r="L90" s="24"/>
+    </row>
+    <row r="91" spans="1:12" ht="195" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -4632,9 +4909,12 @@
         <v>1</v>
       </c>
       <c r="J91" s="38"/>
-      <c r="K91" s="24"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K91" s="36">
+        <v>0</v>
+      </c>
+      <c r="L91" s="24"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -4660,9 +4940,12 @@
       <c r="J92" s="20">
         <v>0</v>
       </c>
-      <c r="K92" s="24"/>
-    </row>
-    <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="K92" s="36">
+        <v>0</v>
+      </c>
+      <c r="L92" s="24"/>
+    </row>
+    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -4694,11 +4977,14 @@
       <c r="J93" s="8">
         <v>5000</v>
       </c>
-      <c r="K93" s="9" t="s">
+      <c r="K93" s="36">
+        <v>0</v>
+      </c>
+      <c r="L93" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -4730,9 +5016,12 @@
       <c r="J94" s="20">
         <v>0</v>
       </c>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="K94" s="36">
+        <v>0</v>
+      </c>
+      <c r="L94" s="9"/>
+    </row>
+    <row r="95" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -4764,9 +5053,12 @@
       <c r="J95" s="8">
         <v>1500</v>
       </c>
-      <c r="K95" s="9"/>
-    </row>
-    <row r="96" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K95" s="36">
+        <v>0</v>
+      </c>
+      <c r="L95" s="9"/>
+    </row>
+    <row r="96" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -4798,9 +5090,12 @@
       <c r="J96" s="16">
         <v>2500</v>
       </c>
-      <c r="K96" s="9"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K96" s="36">
+        <v>0</v>
+      </c>
+      <c r="L96" s="9"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -4830,9 +5125,12 @@
       <c r="J97" s="16">
         <v>2500</v>
       </c>
-      <c r="K97" s="9"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K97" s="36">
+        <v>0</v>
+      </c>
+      <c r="L97" s="9"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -4860,9 +5158,12 @@
       <c r="J98" s="17">
         <v>0</v>
       </c>
-      <c r="K98" s="9"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K98" s="36">
+        <v>0</v>
+      </c>
+      <c r="L98" s="9"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -4876,9 +5177,10 @@
       <c r="H99" s="16"/>
       <c r="I99" s="16"/>
       <c r="J99" s="16"/>
-      <c r="K99" s="9"/>
-    </row>
-    <row r="101" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K99" s="16"/>
+      <c r="L99" s="9"/>
+    </row>
+    <row r="101" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C101" s="27" t="s">
         <v>136</v>
       </c>
@@ -4889,8 +5191,9 @@
       <c r="H101" s="29"/>
       <c r="I101" s="29"/>
       <c r="J101" s="29"/>
-    </row>
-    <row r="102" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K101" s="29"/>
+    </row>
+    <row r="102" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C102" s="28"/>
       <c r="D102" s="28"/>
       <c r="E102" s="28"/>
@@ -4899,8 +5202,9 @@
       <c r="H102" s="29"/>
       <c r="I102" s="29"/>
       <c r="J102" s="29"/>
-    </row>
-    <row r="103" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K102" s="29"/>
+    </row>
+    <row r="103" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D103" s="28"/>
       <c r="E103" s="30" t="s">
         <v>137</v>
@@ -4919,14 +5223,18 @@
       </c>
       <c r="I103" s="32">
         <f>COUNTIFS(E2:E98, "House", I2:I98, "&lt;&gt;0")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J103" s="32">
         <f>COUNTIFS(E2:E98, "House", J2:J98, "&lt;&gt;0")</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="K103" s="32">
+        <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D104" s="28"/>
       <c r="E104" s="30" t="s">
         <v>138</v>
@@ -4949,36 +5257,44 @@
       </c>
       <c r="J104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", J2:J98, "&lt;&gt;0")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="K104" s="32">
+        <f>COUNTIFS(E2:E98, "Apartment", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D105" s="28"/>
       <c r="E105" s="30" t="s">
         <v>139</v>
       </c>
       <c r="F105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", F2:F98, "&lt;&gt;0")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", G2:G98, "&lt;&gt;0.00")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", H2:H98, "&lt;&gt;0")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", I2:I98, "&lt;&gt;0")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", J2:J98, "&lt;&gt;0")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="K105" s="32">
+        <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C106" s="33"/>
       <c r="D106" s="28"/>
       <c r="E106" s="28"/>
@@ -4987,17 +5303,18 @@
       <c r="H106" s="34"/>
       <c r="I106" s="34"/>
       <c r="J106" s="34"/>
-    </row>
-    <row r="108" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K106" s="34"/>
+    </row>
+    <row r="108" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="K108" s="37"/>
-    </row>
-    <row r="109" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="L108" s="37"/>
+    </row>
+    <row r="109" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C109" s="31"/>
     </row>
-    <row r="110" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E110" s="31" t="s">
         <v>23</v>
       </c>
@@ -5021,8 +5338,12 @@
         <f>COUNTIFS(D2:D98, "1st Main", J2:J98, "&lt;&gt;0")</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K110" s="32">
+        <f>COUNTIFS(D2:D98, "1st Main", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E111" s="31" t="s">
         <v>34</v>
       </c>
@@ -5046,8 +5367,12 @@
         <f>COUNTIFS(D2:D98, "2nd Main", J2:J98, "&lt;&gt;0")</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K111" s="32">
+        <f>COUNTIFS(D2:D98, "2nd Main", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E112" s="31" t="s">
         <v>31</v>
       </c>
@@ -5069,10 +5394,14 @@
       </c>
       <c r="J112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", J2:J98, "&lt;&gt;0")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="5:10" ht="18.75" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K112" s="32">
+        <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E113" s="31" t="s">
         <v>41</v>
       </c>
@@ -5096,8 +5425,12 @@
         <f>COUNTIFS(D2:D98, "1st Cross", J2:J98, "&lt;&gt;0")</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="5:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K113" s="32">
+        <f>COUNTIFS(D2:D98, "1st Cross", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E114" s="31" t="s">
         <v>21</v>
       </c>
@@ -5121,8 +5454,12 @@
         <f>COUNTIFS(D2:D98, "2nd Cross", J2:J98, "&lt;&gt;0")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="5:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K114" s="32">
+        <f>COUNTIFS(D2:D98, "2nd Cross", K2:K98, "&lt;&gt;0")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E115" s="31" t="s">
         <v>17</v>
       </c>
@@ -5146,33 +5483,41 @@
         <f>COUNTIFS(D2:D98, "3rd Cross", J2:J98, "&lt;&gt;0")</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="116" spans="5:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K115" s="32">
+        <f>COUNTIFS(D2:D98, "3rd Cross", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E116" s="31" t="s">
         <v>58</v>
       </c>
       <c r="F116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", F2:F98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", G2:G98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", H2:H98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", I2:I98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J116" s="32">
         <f>COUNTIFS(D2:D98, "4th Cross", J2:J98, "&lt;&gt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="5:10" ht="18.75" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="K116" s="32">
+        <f>COUNTIFS(D2:D98, "4th Cross", K2:K98, "&lt;&gt;0")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E117" s="31" t="s">
         <v>10</v>
       </c>
@@ -5196,9 +5541,13 @@
         <f>COUNTIFS(D2:D98, "Seethammal Road", J2:J98, "&lt;&gt;0")</f>
         <v>15</v>
       </c>
+      <c r="K117" s="32">
+        <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K98">
+  <autoFilter ref="A1:L98">
     <sortState ref="A2:J96">
       <sortCondition ref="D1:D96"/>
     </sortState>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -2282,8 +2282,8 @@
       <c r="J22" s="18">
         <v>2500</v>
       </c>
-      <c r="K22" s="36">
-        <v>0</v>
+      <c r="K22" s="18">
+        <v>2500</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>172</v>
@@ -2536,8 +2536,8 @@
       <c r="J28" s="9">
         <v>2500</v>
       </c>
-      <c r="K28" s="36">
-        <v>0</v>
+      <c r="K28" s="18">
+        <v>2500</v>
       </c>
       <c r="L28" s="9"/>
       <c r="M28" s="10"/>
@@ -2694,8 +2694,8 @@
       <c r="J32" s="22">
         <v>1500</v>
       </c>
-      <c r="K32" s="36">
-        <v>0</v>
+      <c r="K32" s="18">
+        <v>1500</v>
       </c>
       <c r="L32" s="24"/>
       <c r="M32" s="10"/>
@@ -3620,8 +3620,8 @@
       <c r="J55" s="8">
         <v>7500</v>
       </c>
-      <c r="K55" s="36">
-        <v>0</v>
+      <c r="K55" s="18">
+        <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
         <v>201</v>
@@ -3954,8 +3954,8 @@
       <c r="J64" s="9">
         <v>2500</v>
       </c>
-      <c r="K64" s="36">
-        <v>0</v>
+      <c r="K64" s="18">
+        <v>2500</v>
       </c>
       <c r="L64" s="9"/>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="K111" s="32">
         <f>COUNTIFS(D2:D98, "2nd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="K115" s="32">
         <f>COUNTIFS(D2:D98, "3rd Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -3452,8 +3452,8 @@
       <c r="J51" s="36">
         <v>0</v>
       </c>
-      <c r="K51" s="36">
-        <v>0</v>
+      <c r="K51" s="18">
+        <v>3000</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="10"/>
@@ -4613,8 +4613,8 @@
       <c r="J83" s="18">
         <v>2500</v>
       </c>
-      <c r="K83" s="36">
-        <v>0</v>
+      <c r="K83" s="18">
+        <v>2500</v>
       </c>
       <c r="L83" s="9"/>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -610,9 +610,6 @@
     <t>Senniappan</t>
   </si>
   <si>
-    <t>Flat 3rd Main Road</t>
-  </si>
-  <si>
     <t>2500 Subcription + Newsletter 3000</t>
   </si>
   <si>
@@ -794,6 +791,10 @@
   </si>
   <si>
     <t>Nandakumar</t>
+  </si>
+  <si>
+    <t>Flat 3rd Main Road
+Brother-in-law of Dr Sankarram</t>
   </si>
 </sst>
 </file>
@@ -1417,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>8</v>
@@ -1502,11 +1503,11 @@
       <c r="J3" s="18">
         <v>7500</v>
       </c>
-      <c r="K3" s="36">
-        <v>0</v>
+      <c r="K3" s="18">
+        <v>7500</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="11"/>
@@ -1550,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
@@ -1674,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="11"/>
@@ -1688,7 +1689,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
@@ -1815,7 +1816,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>23</v>
@@ -1838,8 +1839,8 @@
       <c r="J11" s="9">
         <v>2500</v>
       </c>
-      <c r="K11" s="36">
-        <v>0</v>
+      <c r="K11" s="18">
+        <v>2500</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="10"/>
@@ -1884,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="11"/>
@@ -1898,7 +1899,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
@@ -1928,7 +1929,7 @@
         <v>2500</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
@@ -1972,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="11"/>
@@ -1986,10 +1987,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" s="48" t="s">
         <v>34</v>
@@ -1998,16 +1999,16 @@
         <v>103</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J15" s="9">
         <v>1500</v>
@@ -2028,10 +2029,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" s="48" t="s">
         <v>34</v>
@@ -2062,10 +2063,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D17" s="48" t="s">
         <v>34</v>
@@ -2138,7 +2139,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>130</v>
@@ -2180,10 +2181,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D20" s="48" t="s">
         <v>34</v>
@@ -2238,7 +2239,7 @@
         <v>1500</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K21" s="36">
         <v>0</v>
@@ -2286,7 +2287,7 @@
         <v>2500</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="11"/>
@@ -2594,10 +2595,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="52" t="s">
         <v>188</v>
-      </c>
-      <c r="C30" s="52" t="s">
-        <v>189</v>
       </c>
       <c r="D30" s="48"/>
       <c r="E30" s="48"/>
@@ -2624,7 +2625,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>109</v>
@@ -2654,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="11"/>
@@ -2794,7 +2795,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>120</v>
@@ -2878,7 +2879,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="41"/>
@@ -2934,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="11"/>
@@ -2978,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="11"/>
@@ -3022,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
@@ -3036,7 +3037,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C41" s="40"/>
       <c r="D41" s="41"/>
@@ -3062,7 +3063,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C42" s="40"/>
       <c r="D42" s="41"/>
@@ -3202,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
@@ -3449,11 +3450,11 @@
       <c r="I51" s="18">
         <v>2500</v>
       </c>
-      <c r="J51" s="36">
-        <v>0</v>
-      </c>
-      <c r="K51" s="18">
-        <v>3000</v>
+      <c r="J51" s="18">
+        <v>7500</v>
+      </c>
+      <c r="K51" s="36">
+        <v>0</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="10"/>
@@ -3552,7 +3553,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>115</v>
@@ -3624,7 +3625,7 @@
         <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
@@ -3668,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="11"/>
@@ -3676,7 +3677,7 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="12"/>
     </row>
-    <row r="57" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3685,7 +3686,7 @@
         <v>144</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>31</v>
@@ -3705,11 +3706,11 @@
       <c r="I57" s="20">
         <v>0</v>
       </c>
-      <c r="J57" s="20">
-        <v>0</v>
-      </c>
-      <c r="K57" s="36">
-        <v>0</v>
+      <c r="J57" s="8">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="18">
+        <v>1500</v>
       </c>
       <c r="L57" s="9"/>
       <c r="M57" s="10"/>
@@ -3724,7 +3725,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="41"/>
@@ -3750,7 +3751,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="41"/>
@@ -3776,7 +3777,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="41"/>
@@ -3844,10 +3845,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="D62" s="48" t="s">
         <v>58</v>
@@ -3909,8 +3910,8 @@
       <c r="I63" s="18">
         <v>2500</v>
       </c>
-      <c r="J63" s="36">
-        <v>0</v>
+      <c r="J63" s="18">
+        <v>2500</v>
       </c>
       <c r="K63" s="36">
         <v>0</v>
@@ -3965,7 +3966,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>78</v>
@@ -4002,10 +4003,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>58</v>
@@ -4014,16 +4015,16 @@
         <v>103</v>
       </c>
       <c r="F66" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G66" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H66" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I66" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J66" s="56"/>
       <c r="K66" s="8">
@@ -4037,7 +4038,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>118</v>
@@ -4077,7 +4078,7 @@
         <v>125</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>50</v>
@@ -4114,7 +4115,7 @@
         <v>61</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>11</v>
@@ -4174,11 +4175,11 @@
       <c r="J70" s="9">
         <v>25000</v>
       </c>
-      <c r="K70" s="36">
-        <v>0</v>
+      <c r="K70" s="18">
+        <v>7500</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4261,7 +4262,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>19</v>
@@ -4362,7 +4363,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -4510,7 +4511,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="41"/>
@@ -4531,28 +4532,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="C81" s="40" t="s">
-        <v>159</v>
-      </c>
       <c r="D81" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E81" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H81" s="42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J81" s="42"/>
       <c r="K81" s="36">
@@ -4566,7 +4567,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="41"/>
@@ -4624,7 +4625,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>141</v>
@@ -4650,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4689,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4765,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4885,7 +4886,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>112</v>
@@ -4920,10 +4921,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>11</v>
@@ -4951,10 +4952,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>11</v>
@@ -4981,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -4993,7 +4994,7 @@
         <v>24</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>11</v>
@@ -5027,10 +5028,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>11</v>
@@ -5064,10 +5065,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="C96" s="54" t="s">
         <v>179</v>
-      </c>
-      <c r="C96" s="54" t="s">
-        <v>180</v>
       </c>
       <c r="D96" s="55" t="s">
         <v>31</v>
@@ -5076,13 +5077,13 @@
         <v>12</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I96" s="16">
         <v>2500</v>
@@ -5101,7 +5102,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="48" t="s">
@@ -5136,7 +5137,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="48"/>
@@ -5227,11 +5228,11 @@
       </c>
       <c r="J103" s="32">
         <f>COUNTIFS(E2:E98, "House", J2:J98, "&lt;&gt;0")</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5261,7 +5262,7 @@
       </c>
       <c r="K104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5287,11 +5288,11 @@
       </c>
       <c r="J105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", J2:J98, "&lt;&gt;0")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5340,7 +5341,7 @@
       </c>
       <c r="K110" s="32">
         <f>COUNTIFS(D2:D98, "1st Main", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5394,7 +5395,7 @@
       </c>
       <c r="J112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", J2:J98, "&lt;&gt;0")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K112" s="32">
         <f>COUNTIFS(D2:D98, "3rd Main", K2:K98, "&lt;&gt;0")</f>
@@ -5427,7 +5428,7 @@
       </c>
       <c r="K113" s="32">
         <f>COUNTIFS(D2:D98, "1st Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5543,7 +5544,7 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="208">
   <si>
     <t>S No</t>
   </si>
@@ -731,9 +731,6 @@
     <t>2A Rathna Apt, Neethirajan P</t>
   </si>
   <si>
-    <t>1A, Rathna Apart, ECM Guptha</t>
-  </si>
-  <si>
     <t>1B Rathna Apartment, S Daniel</t>
   </si>
   <si>
@@ -795,6 +792,22 @@
   <si>
     <t>Flat 3rd Main Road
 Brother-in-law of Dr Sankarram</t>
+  </si>
+  <si>
+    <t>1A, Rathna Apart, ECM Guptha
+Chandramauleeswara Gupta</t>
+  </si>
+  <si>
+    <t>Narayanaswamy Ravichandran</t>
+  </si>
+  <si>
+    <t>Old 61 New 16, Seethamma Road</t>
+  </si>
+  <si>
+    <t>Syed Khalid Hussein</t>
+  </si>
+  <si>
+    <t>8 First Main Road</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1437,7 @@
         <v>180</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>8</v>
@@ -1507,7 +1520,7 @@
         <v>7500</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="11"/>
@@ -1547,8 +1560,8 @@
       <c r="J4" s="35">
         <v>0</v>
       </c>
-      <c r="K4" s="36">
-        <v>0</v>
+      <c r="K4" s="18">
+        <v>2500</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>169</v>
@@ -1881,8 +1894,8 @@
       <c r="J12" s="8">
         <v>2500</v>
       </c>
-      <c r="K12" s="36">
-        <v>0</v>
+      <c r="K12" s="18">
+        <v>2500</v>
       </c>
       <c r="L12" s="24" t="s">
         <v>167</v>
@@ -1929,7 +1942,7 @@
         <v>2500</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
@@ -1981,13 +1994,13 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="12"/>
     </row>
-    <row r="15" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C15" s="52" t="s">
         <v>182</v>
@@ -2013,8 +2026,8 @@
       <c r="J15" s="9">
         <v>1500</v>
       </c>
-      <c r="K15" s="36">
-        <v>0</v>
+      <c r="K15" s="18">
+        <v>1250</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="10"/>
@@ -2047,8 +2060,8 @@
       <c r="J16" s="9">
         <v>1500</v>
       </c>
-      <c r="K16" s="36">
-        <v>0</v>
+      <c r="K16" s="18">
+        <v>1250</v>
       </c>
       <c r="L16" s="9"/>
       <c r="M16" s="10"/>
@@ -2063,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>182</v>
@@ -2181,7 +2194,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C20" s="52" t="s">
         <v>182</v>
@@ -2412,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="36">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L25" s="24"/>
       <c r="M25" s="10"/>
@@ -2595,17 +2608,27 @@
         <v>29</v>
       </c>
       <c r="B30" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="48"/>
+      <c r="D30" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="E30" s="48"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
       <c r="J30" s="9">
         <v>7500</v>
       </c>
@@ -2821,8 +2844,8 @@
       <c r="J35" s="8">
         <v>1500</v>
       </c>
-      <c r="K35" s="36">
-        <v>0</v>
+      <c r="K35" s="18">
+        <v>1500</v>
       </c>
       <c r="L35" s="24"/>
       <c r="M35" s="10"/>
@@ -2874,25 +2897,39 @@
       <c r="Q36" s="12"/>
     </row>
     <row r="37" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="39">
+      <c r="A37" s="51">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="36">
-        <v>0</v>
-      </c>
-      <c r="L37" s="44"/>
+      <c r="B37" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="48"/>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>2500</v>
+      </c>
+      <c r="L37" s="50"/>
       <c r="M37" s="10"/>
       <c r="N37" s="11"/>
       <c r="O37" s="11"/>
@@ -2935,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="11"/>
@@ -3023,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
@@ -3058,25 +3095,33 @@
       <c r="Q41" s="12"/>
     </row>
     <row r="42" spans="1:17" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39">
+      <c r="A42" s="55">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B42" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="36">
-        <v>0</v>
-      </c>
-      <c r="L42" s="42"/>
+      <c r="B42" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="18">
+        <v>2500</v>
+      </c>
+      <c r="L42" s="9"/>
       <c r="M42" s="10"/>
       <c r="N42" s="11"/>
       <c r="O42" s="11"/>
@@ -3203,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
@@ -3625,7 +3670,7 @@
         <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
@@ -3686,7 +3731,7 @@
         <v>144</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>31</v>
@@ -3913,8 +3958,8 @@
       <c r="J63" s="18">
         <v>2500</v>
       </c>
-      <c r="K63" s="36">
-        <v>0</v>
+      <c r="K63" s="18">
+        <v>2500</v>
       </c>
       <c r="L63" s="9"/>
       <c r="M63" s="10"/>
@@ -4003,7 +4048,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C66" s="54" t="s">
         <v>164</v>
@@ -4138,8 +4183,8 @@
       <c r="J69" s="8">
         <v>2500</v>
       </c>
-      <c r="K69" s="36">
-        <v>0</v>
+      <c r="K69" s="18">
+        <v>2512</v>
       </c>
       <c r="L69" s="9"/>
     </row>
@@ -4179,7 +4224,7 @@
         <v>7500</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4262,7 +4307,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>19</v>
@@ -4352,8 +4397,8 @@
       <c r="J75" s="9">
         <v>10000</v>
       </c>
-      <c r="K75" s="36">
-        <v>0</v>
+      <c r="K75" s="18">
+        <v>10000</v>
       </c>
       <c r="L75" s="9"/>
     </row>
@@ -4386,11 +4431,11 @@
       <c r="I76" s="9">
         <v>2500</v>
       </c>
-      <c r="J76" s="35">
-        <v>0</v>
-      </c>
-      <c r="K76" s="36">
-        <v>0</v>
+      <c r="J76" s="9">
+        <v>0</v>
+      </c>
+      <c r="K76" s="18">
+        <v>2500</v>
       </c>
       <c r="L76" s="9"/>
     </row>
@@ -4625,7 +4670,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>141</v>
@@ -4651,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4686,8 +4731,8 @@
       <c r="J85" s="36">
         <v>0</v>
       </c>
-      <c r="K85" s="36">
-        <v>0</v>
+      <c r="K85" s="18">
+        <v>2500</v>
       </c>
       <c r="L85" s="9" t="s">
         <v>175</v>
@@ -4875,8 +4920,8 @@
       <c r="J90" s="8">
         <v>7500</v>
       </c>
-      <c r="K90" s="36">
-        <v>0</v>
+      <c r="K90" s="18">
+        <v>7500</v>
       </c>
       <c r="L90" s="24"/>
     </row>
@@ -4982,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -5102,7 +5147,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="48" t="s">
@@ -5159,8 +5204,8 @@
       <c r="J98" s="17">
         <v>0</v>
       </c>
-      <c r="K98" s="36">
-        <v>0</v>
+      <c r="K98" s="18">
+        <v>1250</v>
       </c>
       <c r="L98" s="9"/>
     </row>
@@ -5212,27 +5257,27 @@
       </c>
       <c r="F103" s="32">
         <f>COUNTIFS(E2:E98, "House", F2:F98, "&lt;&gt;0")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G103" s="32">
         <f>COUNTIFS(E2:E98, "House", G2:G98, "&lt;&gt;0")</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H103" s="32">
         <f>COUNTIFS(E2:E98, "House", H2:H98, "&lt;&gt;0")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I103" s="32">
         <f>COUNTIFS(E2:E98, "House", I2:I98, "&lt;&gt;0")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J103" s="32">
         <f>COUNTIFS(E2:E98, "House", J2:J98, "&lt;&gt;0")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5262,7 +5307,7 @@
       </c>
       <c r="K104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5292,7 +5337,7 @@
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5341,7 +5386,7 @@
       </c>
       <c r="K110" s="32">
         <f>COUNTIFS(D2:D98, "1st Main", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5370,7 +5415,7 @@
       </c>
       <c r="K111" s="32">
         <f>COUNTIFS(D2:D98, "2nd Main", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5428,7 +5473,7 @@
       </c>
       <c r="K113" s="32">
         <f>COUNTIFS(D2:D98, "1st Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5486,7 +5531,7 @@
       </c>
       <c r="K115" s="32">
         <f>COUNTIFS(D2:D98, "3rd Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5524,27 +5569,27 @@
       </c>
       <c r="F117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", F2:F98, "&lt;&gt;0")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", G2:G98, "&lt;&gt;0")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", H2:H98, "&lt;&gt;0")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", I2:I98, "&lt;&gt;0")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", J2:J98, "&lt;&gt;0")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -5023,8 +5023,8 @@
       <c r="J93" s="8">
         <v>5000</v>
       </c>
-      <c r="K93" s="36">
-        <v>0</v>
+      <c r="K93" s="18">
+        <v>1500</v>
       </c>
       <c r="L93" s="9" t="s">
         <v>191</v>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="K105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", K2:K98, "&lt;&gt;0")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/scra/scra_pymt_history_from_2021.xlsx
+++ b/scra/scra_pymt_history_from_2021.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="207">
   <si>
     <t>S No</t>
   </si>
@@ -298,9 +298,6 @@
   </si>
   <si>
     <t>1st Cross Street</t>
-  </si>
-  <si>
-    <t>S Padmanabhan</t>
   </si>
   <si>
     <t>Malavika Apartment</t>
@@ -1431,13 +1428,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>8</v>
@@ -1474,8 +1471,8 @@
       <c r="J2" s="18">
         <v>2500</v>
       </c>
-      <c r="K2" s="36">
-        <v>0</v>
+      <c r="K2" s="18">
+        <v>2500</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="10"/>
@@ -1520,7 +1517,7 @@
         <v>7500</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="11"/>
@@ -1564,7 +1561,7 @@
         <v>2500</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
@@ -1580,7 +1577,7 @@
         <v>73</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>41</v>
@@ -1601,8 +1598,8 @@
       <c r="J5" s="9">
         <v>10000</v>
       </c>
-      <c r="K5" s="36">
-        <v>0</v>
+      <c r="K5" s="18">
+        <v>10000</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
@@ -1616,10 +1613,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>41</v>
@@ -1658,16 +1655,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -1688,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="11"/>
@@ -1702,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>22</v>
@@ -1826,10 +1823,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>23</v>
@@ -1868,10 +1865,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>23</v>
@@ -1898,7 +1895,7 @@
         <v>2500</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="11"/>
@@ -1912,7 +1909,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
@@ -1942,7 +1939,7 @@
         <v>2500</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
@@ -1986,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="11"/>
@@ -2000,28 +1997,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" s="48" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J15" s="9">
         <v>1500</v>
@@ -2042,16 +2039,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D16" s="48" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -2076,16 +2073,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17" s="48" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
@@ -2110,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>20</v>
@@ -2152,10 +2149,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>21</v>
@@ -2194,16 +2191,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D20" s="48" t="s">
         <v>34</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2252,7 +2249,7 @@
         <v>1500</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K21" s="36">
         <v>0</v>
@@ -2300,7 +2297,7 @@
         <v>2500</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="11"/>
@@ -2314,16 +2311,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -2356,10 +2353,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>34</v>
@@ -2398,16 +2395,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2440,10 +2437,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>34</v>
@@ -2566,10 +2563,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>17</v>
@@ -2608,10 +2605,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="52" t="s">
         <v>186</v>
-      </c>
-      <c r="C30" s="52" t="s">
-        <v>187</v>
       </c>
       <c r="D30" s="48" t="s">
         <v>11</v>
@@ -2648,10 +2645,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>17</v>
@@ -2678,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="11"/>
@@ -2692,16 +2689,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F32" s="8">
         <v>0</v>
@@ -2734,16 +2731,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2776,16 +2773,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F34" s="8">
         <v>0</v>
@@ -2818,16 +2815,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2860,16 +2857,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="8">
         <v>0</v>
@@ -2902,10 +2899,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="52" t="s">
         <v>206</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>207</v>
       </c>
       <c r="D37" s="48" t="s">
         <v>23</v>
@@ -2972,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="11"/>
@@ -3016,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="11"/>
@@ -3060,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
@@ -3074,7 +3071,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="40"/>
       <c r="D41" s="41"/>
@@ -3100,10 +3097,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="54" t="s">
         <v>204</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>205</v>
       </c>
       <c r="D42" s="55" t="s">
         <v>11</v>
@@ -3218,7 +3215,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>30</v>
@@ -3248,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
@@ -3262,10 +3259,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>31</v>
@@ -3304,10 +3301,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>31</v>
@@ -3346,10 +3343,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>31</v>
@@ -3388,10 +3385,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>31</v>
@@ -3430,10 +3427,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>31</v>
@@ -3472,7 +3469,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>30</v>
@@ -3514,10 +3511,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>31</v>
@@ -3556,7 +3553,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>30</v>
@@ -3598,10 +3595,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>31</v>
@@ -3640,10 +3637,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>31</v>
@@ -3670,7 +3667,7 @@
         <v>2500</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
@@ -3684,10 +3681,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>31</v>
@@ -3714,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="11"/>
@@ -3728,16 +3725,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F57" s="8">
         <v>0</v>
@@ -3770,7 +3767,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C58" s="40"/>
       <c r="D58" s="41"/>
@@ -3796,7 +3793,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C59" s="40"/>
       <c r="D59" s="41"/>
@@ -3822,7 +3819,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" s="40"/>
       <c r="D60" s="41"/>
@@ -3890,16 +3887,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="D62" s="48" t="s">
         <v>58</v>
       </c>
       <c r="E62" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F62" s="16">
         <v>0</v>
@@ -4011,10 +4008,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>50</v>
@@ -4048,28 +4045,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>58</v>
       </c>
       <c r="E66" s="55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F66" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G66" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H66" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I66" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J66" s="56"/>
       <c r="K66" s="8">
@@ -4083,10 +4080,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>50</v>
@@ -4120,10 +4117,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>50</v>
@@ -4160,7 +4157,7 @@
         <v>61</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>11</v>
@@ -4224,7 +4221,7 @@
         <v>7500</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -4279,7 +4276,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F72" s="8">
         <v>10000</v>
@@ -4307,7 +4304,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>19</v>
@@ -4316,7 +4313,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="20"/>
@@ -4408,7 +4405,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -4556,7 +4553,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C80" s="40"/>
       <c r="D80" s="41"/>
@@ -4577,28 +4574,28 @@
         <v>80</v>
       </c>
       <c r="B81" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="C81" s="40" t="s">
-        <v>158</v>
-      </c>
       <c r="D81" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E81" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F81" s="38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H81" s="42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J81" s="42"/>
       <c r="K81" s="36">
@@ -4612,7 +4609,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C82" s="40"/>
       <c r="D82" s="41"/>
@@ -4670,10 +4667,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>11</v>
@@ -4696,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4705,10 +4702,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>11</v>
@@ -4735,7 +4732,7 @@
         <v>2500</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4744,10 +4741,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>11</v>
@@ -4781,7 +4778,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>10</v>
@@ -4807,11 +4804,11 @@
       <c r="J87" s="9">
         <v>2500</v>
       </c>
-      <c r="K87" s="36">
-        <v>0</v>
+      <c r="K87" s="18">
+        <v>2500</v>
       </c>
       <c r="L87" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4820,10 +4817,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>11</v>
@@ -4857,7 +4854,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
@@ -4894,10 +4891,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>11</v>
@@ -4931,10 +4928,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>11</v>
@@ -4966,16 +4963,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F92" s="20"/>
       <c r="G92" s="20"/>
@@ -4997,16 +4994,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F93" s="20">
         <v>0</v>
@@ -5027,7 +5024,7 @@
         <v>1500</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -5039,13 +5036,13 @@
         <v>24</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F94" s="20">
         <v>0</v>
@@ -5073,16 +5070,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F95" s="20">
         <v>0</v>
@@ -5110,10 +5107,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="54" t="s">
         <v>178</v>
-      </c>
-      <c r="C96" s="54" t="s">
-        <v>179</v>
       </c>
       <c r="D96" s="55" t="s">
         <v>31</v>
@@ -5122,13 +5119,13 @@
         <v>12</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I96" s="16">
         <v>2500</v>
@@ -5147,7 +5144,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="48" t="s">
@@ -5182,12 +5179,12 @@
         <v>97</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="48"/>
       <c r="E98" s="48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F98" s="17">
         <v>0</v>
@@ -5228,7 +5225,7 @@
     </row>
     <row r="101" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C101" s="27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D101" s="28"/>
       <c r="E101" s="28"/>
@@ -5253,7 +5250,7 @@
     <row r="103" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D103" s="28"/>
       <c r="E103" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F103" s="32">
         <f>COUNTIFS(E2:E98, "House", F2:F98, "&lt;&gt;0")</f>
@@ -5277,13 +5274,13 @@
       </c>
       <c r="K103" s="32">
         <f>COUNTIFS(E2:E98, "House", K2:K98, "&lt;&gt;0")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D104" s="28"/>
       <c r="E104" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F104" s="32">
         <f>COUNTIFS(E2:E98, "Apartment", F2:F98, "&lt;&gt;0")</f>
@@ -5313,7 +5310,7 @@
     <row r="105" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D105" s="28"/>
       <c r="E105" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F105" s="32">
         <f>COUNTIFS(E2:E98, "Ind. Apartment", F2:F98, "&lt;&gt;0")</f>
@@ -5353,7 +5350,7 @@
     </row>
     <row r="108" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L108" s="37"/>
     </row>
@@ -5473,7 +5470,7 @@
       </c>
       <c r="K113" s="32">
         <f>COUNTIFS(D2:D98, "1st Cross", K2:K98, "&lt;&gt;0")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="5:11" ht="18.75" x14ac:dyDescent="0.3">
@@ -5589,7 +5586,7 @@
       </c>
       <c r="K117" s="32">
         <f>COUNTIFS(D2:D98, "Seethammal Road", K2:K98, "&lt;&gt;0")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
